--- a/views/open_accountability_ledger.xlsx
+++ b/views/open_accountability_ledger.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lenses &amp; legend" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Entries'!$A$3:$M$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Entries'!$A$3:$M$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -155,6 +155,9 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
@@ -165,9 +168,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -563,14 +563,14 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Accountability Ledger — register v0.1.0 · build-phase demonstrator, internal, not for publication</t>
+          <t>Open Accountability Ledger — register v0.4.0 · build-phase demonstrator, internal, not for publication</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>JSON is the source of truth. Columns public_use and hold_reason are AUTO-derived (status UNVERIFIED or confidence LOW → held). Edit status/confidence, not the derived columns; then regenerate.</t>
+          <t>JSON is the source of truth. Columns public_use and hold_reason are AUTO-derived (status UNVERIFIED or LIVE, or confidence LOW, are held). Edit status/confidence, not the derived columns; then regenerate.</t>
         </is>
       </c>
     </row>
@@ -929,72 +929,68 @@
       <c r="M8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C9" s="11" t="inlineStr">
-        <is>
-          <t>Cowaramup service station, warned live, decision pending</t>
-        </is>
-      </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>A 12-bay service station is before an unelected Development Assessment Panel; 100+ residents protested on the safety grounds the town's own Precinct Plan already flags.</t>
-        </is>
-      </c>
-      <c r="E9" s="11" t="inlineStr">
-        <is>
-          <t>Live, decision NOT yet made. In 2017 a servo drew 297 objections and was rejected, yet a truckstop operates there now. Not an “override” yet.</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>UNVERIFIED</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr"/>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Container deposit scheme (wine), warned, launched anyway</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>Friends of WA Wine put it in writing: ~$1.15 to 1.25 real cost per bottle vs a 10c refund, ~$11m/yr for under 1% litter gain, no WA glass reprocessor, WA hit a year early. They asked for a pause.</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Government launched on schedule; the cost lands on regional wine country. The strongest of the four, fully documented, Warren-Blackwood's own back yard.</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>IGNORED</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>~$11m/yr industry cost</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="I9" s="11" t="inlineStr">
-        <is>
-          <t>DAP application DAP/26/03096 (Apr 2026); resident protest May 2026</t>
-        </is>
-      </c>
-      <c r="J9" s="12" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="K9" s="13" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="L9" s="11" t="inlineStr">
-        <is>
-          <t>HOLD: not for public use (status UNVERIFIED). Live matter, decision not yet made. Do not present as an override until the DAP determines it.</t>
-        </is>
-      </c>
-      <c r="M9" s="11" t="inlineStr">
-        <is>
-          <t>Live matter, decision not yet made. Do not present as an override until the DAP determines it.</t>
-        </is>
-      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>Friends of WA Wine submission &amp; Minister meeting (Mar 2026)</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K9" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L9" s="9" t="inlineStr"/>
+      <c r="M9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>B3</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
@@ -1004,17 +1000,17 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>Container deposit scheme (wine), warned, launched anyway</t>
+          <t>West Coast demersal fishing, warned 15 years, brutal patch</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Friends of WA Wine put it in writing: ~$1.15 to 1.25 real cost per bottle vs a 10c refund, ~$11m/yr for under 1% litter gain, no WA glass reprocessor, WA hit a year early. They asked for a pause.</t>
+          <t>The fishery ran on an “interim” plan since 2007; overfishing was on the record ~15 years while fixes stayed too small.</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Government launched on schedule; the cost lands on regional wine country. The strongest of the four, fully documented, Warren-Blackwood's own back yard.</t>
+          <t>Dec 2025: rec fishing shut 21 months, commercial demersal permanently closed, $29.2m package. Frame only as “managed too slowly”, the science was right.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
@@ -1024,17 +1020,17 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>~$11m/yr industry cost</t>
+          <t>$29.2m support package</t>
         </is>
       </c>
       <c r="H10" s="5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2007 to 2025</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>Friends of WA Wine submission &amp; Minister meeting (Mar 2026)</t>
+          <t>WA West Coast Demersal Scalefish management; Dec 2025 closure</t>
         </is>
       </c>
       <c r="J10" s="7" t="inlineStr">
@@ -1053,7 +1049,7 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>B3</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
@@ -1063,17 +1059,17 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>West Coast demersal fishing, warned 15 years, brutal patch</t>
+          <t>Sandalwood (FPC to DBCA), warned since 1921</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>The fishery ran on an “interim” plan since 2007; overfishing was on the record ~15 years while fixes stayed too small.</t>
+          <t>WA Forests Dept reports warned in 1921 and 1958 that harvest rates were driving sandalwood to extinction; Red-listed vulnerable in 2021, wild populations down ~90%.</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Dec 2025: rec fishing shut 21 months, commercial demersal permanently closed, $29.2m package. Frame only as “managed too slowly”, the science was right.</t>
+          <t>Control moves to DBCA from 2027 with quota quietly cut ~20%; the FPC blames bettongs and rainfall, never a century of harvest. Confirm handover scope.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -1083,22 +1079,22 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>$29.2m support package</t>
+          <t>quota 2,500t to 2,000t</t>
         </is>
       </c>
       <c r="H11" s="5" t="inlineStr">
         <is>
-          <t>2007 to 2025</t>
+          <t>1921 to 2027</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>WA West Coast Demersal Scalefish management; Dec 2025 closure</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>WA Forests Dept reports 1921 &amp; 1958; IUCN Red List 2021</t>
+        </is>
+      </c>
+      <c r="J11" s="10" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="K11" s="8" t="inlineStr">
@@ -1107,32 +1103,36 @@
         </is>
       </c>
       <c r="L11" s="9" t="inlineStr"/>
-      <c r="M11" s="6" t="inlineStr"/>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>Confirm the FPC to DBCA handover scope before public use.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>B4</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>Sandalwood (FPC to DBCA), warned since 1921</t>
+          <t>Aboriginal Cultural Heritage Act 2021, rushed, repealed in 5 weeks</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>WA Forests Dept reports warned in 1921 and 1958 that harvest rates were driving sandalwood to extinction; Red-listed vulnerable in 2021, wild populations down ~90%.</t>
+          <t>The Act passed both houses in ~5 weeks and came into force 1 July 2023; a ~29,000-signature petition sought delay.</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Control moves to DBCA from 2027 with quota quietly cut ~20%; the FPC blames bettongs and rainfall, never a century of harvest. Confirm handover scope.</t>
+          <t>Repeal announced five weeks after commencement. A rushed process that failed landholders and Aboriginal people alike. A process failure, told evenhandedly.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -1140,105 +1140,89 @@
           <t>IGNORED</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
-          <t>quota 2,500t to 2,000t</t>
-        </is>
-      </c>
+      <c r="G12" s="5" t="inlineStr"/>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>1921 to 2027</t>
+          <t>2021 to 2023</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>WA Forests Dept reports 1921 &amp; 1958; IUCN Red List 2021</t>
-        </is>
-      </c>
-      <c r="J12" s="14" t="inlineStr">
+          <t>Aboriginal Cultural Heritage Act 2021 (WA); repeal 8 Aug 2023</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L12" s="9" t="inlineStr"/>
+      <c r="M12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Native-forest logging ban, industry “blindsided”</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>Government claimed consultation on ending native-forest logging.</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Timber industry and forest towns said they were “blindsided,” learning of a livelihood-reshaping decision through the announcement.</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>IGNORED</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>6PR, industry “blindsided” by native forestry ban</t>
+        </is>
+      </c>
+      <c r="J13" s="10" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K13" s="8" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="L12" s="9" t="inlineStr"/>
-      <c r="M12" s="6" t="inlineStr">
-        <is>
-          <t>Confirm the FPC to DBCA handover scope before public use.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>B5</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
-        <is>
-          <t>CDS regional refund-point access, warned 2018</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>A 2018 warning held that regional and remote communities would struggle to access container refund points.</t>
-        </is>
-      </c>
-      <c r="E13" s="11" t="inlineStr">
-        <is>
-          <t>The warning is real and documented, but we could not confirm it materialised into closures or harm. Held as “worth checking,” not proven.</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>UNVERIFIED</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr"/>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>2018 regional/remote refund-point access warning</t>
-        </is>
-      </c>
-      <c r="J13" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K13" s="13" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="L13" s="11" t="inlineStr">
-        <is>
-          <t>HOLD: not for public use (status UNVERIFIED, confidence LOW). Warning documented but not confirmed to have materialised into harm. Worth checking, not proven.</t>
-        </is>
-      </c>
-      <c r="M13" s="11" t="inlineStr">
-        <is>
-          <t>Warning documented but not confirmed to have materialised into harm. Worth checking, not proven.</t>
-        </is>
-      </c>
+      <c r="L13" s="9" t="inlineStr"/>
+      <c r="M13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C4</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
@@ -1248,17 +1232,17 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>Aboriginal Cultural Heritage Act 2021, rushed, repealed in 5 weeks</t>
+          <t>WA council mergers, government tried to remove the ratepayer vote</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>The Act passed both houses in ~5 weeks and came into force 1 July 2023; a ~29,000-signature petition sought delay.</t>
+          <t>From 2013 the Barnett Government moved to cut Perth's 30 metropolitan councils to around 14 to 16, and sought to suspend the “Dadour” provisions, the electors' statutory right to force a binding poll on a merger. Where mergers would have triggered those polls, it used boundary-change orders that carried no poll right. WALGA called it an “effective removal of the democratic process.”</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Repeal announced five weeks after commencement. A rushed process that failed landholders and Aboriginal people alike. A process failure, told evenhandedly.</t>
+          <t>Ratepayers stopped it, not the government. Where the poll right survived, electors voted on 7 February 2015 and rejected the mergers by 76 to 88 per cent (Kwinana 88% no, South Perth 78%, East Fremantle 76%). The government shelved the program on 17 February 2015.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
@@ -1269,12 +1253,12 @@
       <c r="G14" s="5" t="inlineStr"/>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>2021 to 2023</t>
+          <t>2013 to 2015</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>Aboriginal Cultural Heritage Act 2021 (WA); repeal 8 Aug 2023</t>
+          <t>WA metropolitan local-government amalgamation program; 7 Feb 2015 ratepayer polls; Policy Quarterly, “Local Government Reform in Western Australia”</t>
         </is>
       </c>
       <c r="J14" s="7" t="inlineStr">
@@ -1288,12 +1272,16 @@
         </is>
       </c>
       <c r="L14" s="9" t="inlineStr"/>
-      <c r="M14" s="6" t="inlineStr"/>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>Merger targets shifted across the program's stages; cite the reduction as a range (30 to around 14-16).</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C5</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
@@ -1303,17 +1291,17 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>Native-forest logging ban, industry “blindsided”</t>
+          <t>COVID-era “significant development” pathway cut out councils and the public</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Government claimed consultation on ending native-forest logging.</t>
+          <t>In 2020 the McGowan Government created the Part 17 “significant development” pathway (Planning and Development Amendment Act 2020) as a temporary COVID-recovery measure to fast-track major projects. It sent decisions to the WA Planning Commission, removed local government, and made public consultation discretionary rather than required.</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Timber industry and forest towns said they were “blindsided,” learning of a livelihood-reshaping decision through the announcement.</t>
+          <t>WALGA's 2020 to 2025 review found councils supported only about 30% of pathway applications, against about 90% for Development Assessment Panels and about 99% for locally-decided ones, and found the pathway “removed Local Government from decision making.” The “temporary” pathway was later extended, not lapsed.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
@@ -1324,15 +1312,15 @@
       <c r="G15" s="5" t="inlineStr"/>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2020 to 2025</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>6PR, industry “blindsided” by native forestry ban</t>
-        </is>
-      </c>
-      <c r="J15" s="14" t="inlineStr">
+          <t>Planning and Development Amendment Act 2020 (WA), Part 17; WALGA, Significant Development Pathway 2020 to 2025 Review (Apr 2025)</t>
+        </is>
+      </c>
+      <c r="J15" s="10" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
@@ -1343,197 +1331,189 @@
         </is>
       </c>
       <c r="L15" s="9" t="inlineStr"/>
-      <c r="M15" s="6" t="inlineStr"/>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>Framed as a reform that reduced consultation, not a false “we consulted” claim. Confirm at point of use.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>WA planning reform (2023), claim not yet tested</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>A large reform with extensive official consultation pages; the government presents a thorough process.</t>
-        </is>
-      </c>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>Searching did not surface evidence the windows were tokenistic. Whether lived experience matched needs the primary-source window dates and submission mix. Unverified.</t>
-        </is>
-      </c>
-      <c r="F16" s="10" t="inlineStr">
-        <is>
-          <t>UNVERIFIED</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="inlineStr"/>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>D1</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Deloitte $440k AI report with fabricated citations</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>DEWR paid Deloitte $440,000 to review the automated welfare-penalty system.</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>The report carried a dozen-plus fabricated citations and a made-up Federal Court quote, produced with GPT-4o; caught by an academic. Deloitte repaid just $97,587, under a quarter of the fee.</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>$440,000, refund $97,587</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>2024 to 2025</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>DEWR Assurance Review; AusTender CN4118426; Sen. Pocock (Oct 2025)</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L16" s="9" t="inlineStr"/>
+      <c r="M16" s="6" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>D2</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>PwC tax leaks, partner banned, 12 Senate recs</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>A PwC partner used confidential Treasury information, received while advising government on an incoming anti-avoidance law, to help clients sidestep it.</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>The Tax Practitioners Board terminated his registration; three federal inquiries followed; the Senate committee made 12 recommendations on consulting integrity.</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>RECURRING</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="I16" s="11" t="inlineStr">
-        <is>
-          <t>Planning and Development Amendment Act 2023 (WA)</t>
-        </is>
-      </c>
-      <c r="J16" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K16" s="13" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="L16" s="11" t="inlineStr">
-        <is>
-          <t>HOLD: not for public use (status UNVERIFIED, confidence LOW). Need primary-source consultation window dates and submission mix before any use.</t>
-        </is>
-      </c>
-      <c r="M16" s="11" t="inlineStr">
-        <is>
-          <t>Need primary-source consultation window dates and submission mix before any use.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>C4</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>WA local-government amalgamations, process unverified</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>WA has real history here (the metropolitan program that collapsed after ratepayer rejection is the obvious candidate).</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="inlineStr">
-        <is>
-          <t>Specific consultation-process facts could not be verified in this pass. Needs dedicated primary-source work before any public use.</t>
-        </is>
-      </c>
-      <c r="F17" s="10" t="inlineStr">
-        <is>
-          <t>UNVERIFIED</t>
-        </is>
-      </c>
-      <c r="G17" s="10" t="inlineStr"/>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>various</t>
-        </is>
-      </c>
-      <c r="I17" s="11" t="inlineStr">
-        <is>
-          <t>WA local-government reform / amalgamation program</t>
-        </is>
-      </c>
-      <c r="J17" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K17" s="13" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="L17" s="11" t="inlineStr">
-        <is>
-          <t>HOLD: not for public use (status UNVERIFIED, confidence LOW). Needs dedicated primary-source work before any public use.</t>
-        </is>
-      </c>
-      <c r="M17" s="11" t="inlineStr">
-        <is>
-          <t>Needs dedicated primary-source work before any public use.</t>
-        </is>
-      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Tax Practitioners Board decision; Senate Finance &amp; Public Administration Cttee</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K17" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L17" s="9" t="inlineStr"/>
+      <c r="M17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t>C5</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>Environment Online / COVID-era changes, unverified</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>Plausible candidates for box-ticking consultation on environmental-approval reforms and COVID-era regulatory changes.</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="inlineStr">
-        <is>
-          <t>Each needs its real window, announcement and stakeholder mix checked, not assumed. Plausible but unverified.</t>
-        </is>
-      </c>
-      <c r="F18" s="10" t="inlineStr">
-        <is>
-          <t>UNVERIFIED</t>
-        </is>
-      </c>
-      <c r="G18" s="10" t="inlineStr"/>
-      <c r="H18" s="10" t="inlineStr"/>
-      <c r="I18" s="11" t="inlineStr">
-        <is>
-          <t>WA Environment Online / environmental-approval &amp; COVID-era reforms</t>
-        </is>
-      </c>
-      <c r="J18" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K18" s="13" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="L18" s="11" t="inlineStr">
-        <is>
-          <t>HOLD: not for public use (status UNVERIFIED, confidence LOW). Placeholder candidates. Each needs its real window, announcement and stakeholder mix checked.</t>
-        </is>
-      </c>
-      <c r="M18" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder candidates. Each needs its real window, announcement and stakeholder mix checked.</t>
-        </is>
-      </c>
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>ATO IT contracts blew out $19.06m to $88.11m</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>Six ATO advisor contracts for IT managed services rose from an approved $19.06m to $88.11m; contractors supply roughly half the ATO's annual IT spend.</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>The ANAO found the value-for-money demonstration “deficient”; eight managed-services contracts worth ~$2.5bn over ten years underpin the dependency.</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>OVERDUE</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>$19.06m to $88.11m</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>ANAO, ATO Procurement of IT Managed Services (performance audit)</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L18" s="9" t="inlineStr"/>
+      <c r="M18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>D1</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -1543,37 +1523,37 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>Deloitte $440k AI report with fabricated citations</t>
+          <t>WA's $1.6bn IT blowout, 10 major projects</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>DEWR paid Deloitte $440,000 to review the automated welfare-penalty system.</t>
+          <t>The AG examined 10 major State IT projects estimated at $2.6bn.</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>The report carried a dozen-plus fabricated citations and a made-up Federal Court quote, produced with GPT-4o; caught by an academic. Deloitte repaid just $97,587, under a quarter of the fee.</t>
+          <t>They rose to at least $4.2bn, a $1.6bn / 62% overrun; half at least doubled, 8 of 10 late by 4 to 78 months. $4.2bn is a floor.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>PARTIAL</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>$440,000, refund $97,587</t>
+          <t>$2.6bn to $4.2bn (+62%)</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>2024 to 2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>DEWR Assurance Review; AusTender CN4118426; Sen. Pocock (Oct 2025)</t>
+          <t>WA Auditor General, 2025 Transparency Report - Major IT Projects</t>
         </is>
       </c>
       <c r="J19" s="7" t="inlineStr">
@@ -1587,12 +1567,16 @@
         </is>
       </c>
       <c r="L19" s="9" t="inlineStr"/>
-      <c r="M19" s="6" t="inlineStr"/>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>$4.2bn is a floor, not a total. Never sum ledger figures.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
@@ -1602,17 +1586,17 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>PwC tax leaks, partner banned, 12 Senate recs</t>
+          <t>Queensland Health / IBM payroll, $98m to ~$1.2bn</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>A PwC partner used confidential Treasury information, received while advising government on an incoming anti-avoidance law, to help clients sidestep it.</t>
+          <t>A payroll system project contracted around $98m.</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>The Tax Practitioners Board terminated his registration; three federal inquiries followed; the Senate committee made 12 recommendations on consulting integrity.</t>
+          <t>Blew out to ~$1.2bn over eight years; the Commission of Inquiry called it in the “front rank of failures… may be the worst” and found a “distinct partiality for IBM.”</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -1620,15 +1604,19 @@
           <t>RECURRING</t>
         </is>
       </c>
-      <c r="G20" s="5" t="inlineStr"/>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>$98m to ~$1.2bn</t>
+        </is>
+      </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2013 inquiry</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>Tax Practitioners Board decision; Senate Finance &amp; Public Administration Cttee</t>
+          <t>Queensland Health Payroll Commission of Inquiry (Chesterman), 2013</t>
         </is>
       </c>
       <c r="J20" s="7" t="inlineStr">
@@ -1647,7 +1635,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -1657,37 +1645,37 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>ATO IT contracts blew out $19.06m to $88.11m</t>
+          <t>WA HRMIS health payroll (Deloitte/SAP), $220m and rising</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Six ATO advisor contracts for IT managed services rose from an approved $19.06m to $88.11m; contractors supply roughly half the ATO's annual IT spend.</t>
+          <t>In 2022 Deloitte/SAP won a ~$220m contract to build WA Health's HR/payroll system.</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>The ANAO found the value-for-money demonstration “deficient”; eight managed-services contracts worth ~$2.5bn over ten years underpin the dependency.</t>
+          <t>Now $274.8m, up $39.2m in a single budget, ~90% spent and still drawing funds.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>OVERDUE</t>
+          <t>RECURRING</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>$19.06m to $88.11m</t>
+          <t>$220m to $274.8m</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2022 to 2026</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>ANAO, ATO Procurement of IT Managed Services (performance audit)</t>
+          <t>WA Health/DoF HRMIS contract disclosures; iTnews (2022)</t>
         </is>
       </c>
       <c r="J21" s="7" t="inlineStr">
@@ -1701,12 +1689,16 @@
         </is>
       </c>
       <c r="L21" s="9" t="inlineStr"/>
-      <c r="M21" s="6" t="inlineStr"/>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>$274.8m is a moving figure; re-confirm at point of use.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
@@ -1716,37 +1708,37 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>WA's $1.6bn IT blowout, 10 major projects</t>
+          <t>GovNext-ICT, the $65m savings that never came</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>The AG examined 10 major State IT projects estimated at $2.6bn.</t>
+          <t>The GovNext-ICT program was sold on projected savings of $65m.</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>They rose to at least $4.2bn, a $1.6bn / 62% overrun; half at least doubled, 8 of 10 late by 4 to 78 months. $4.2bn is a floor.</t>
+          <t>The Department of Premier and Cabinet accepted the AG's finding: “little doubt that the projected $65 million savings… will not be achieved.”</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>IGNORED</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>$2.6bn to $4.2bn (+62%)</t>
+          <t>$65m savings never realised</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>WA Auditor General, 2025 Transparency Report - Major IT Projects</t>
+          <t>WA Auditor General, Implementation of the GovNext-ICT Program</t>
         </is>
       </c>
       <c r="J22" s="7" t="inlineStr">
@@ -1760,16 +1752,12 @@
         </is>
       </c>
       <c r="L22" s="9" t="inlineStr"/>
-      <c r="M22" s="6" t="inlineStr">
-        <is>
-          <t>$4.2bn is a floor, not a total. Never sum ledger figures.</t>
-        </is>
-      </c>
+      <c r="M22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D8</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
@@ -1779,42 +1767,42 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>Queensland Health / IBM payroll, $98m to ~$1.2bn</t>
+          <t>Office of Shared Services, ~$370m to unwind</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>A payroll system project contracted around $98m.</t>
+          <t>WA's Office of Shared Services was sold as a savings program.</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Blew out to ~$1.2bn over eight years; the Commission of Inquiry called it in the “front rank of failures… may be the worst” and found a “distinct partiality for IBM.”</t>
+          <t>Scrapped as a costly write-off: ~$370m to unwind after ~$258m had already been spent. Claimed savings became a loss.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>RECURRING</t>
+          <t>IGNORED</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>$98m to ~$1.2bn</t>
+          <t>~$370m to unwind</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>2013 inquiry</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>Queensland Health Payroll Commission of Inquiry (Chesterman), 2013</t>
-        </is>
-      </c>
-      <c r="J23" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>iTnews (2011), “WA to pay $370m to scrap shared services”</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="K23" s="8" t="inlineStr">
@@ -1828,7 +1816,7 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="B24" s="5" t="inlineStr">
@@ -1838,17 +1826,17 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>WA HRMIS health payroll (Deloitte/SAP), $220m and rising</t>
+          <t>WA's consultant shadow, $7.3m reported vs $154.7m real</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>In 2022 Deloitte/SAP won a ~$220m contract to build WA Health's HR/payroll system.</t>
+          <t>WA disclosed just $7.3m of whole-of-government “consultants” (six months to June 2023).</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Now $274.8m, up $39.2m in a single budget, ~90% spent and still drawing funds.</t>
+          <t>One agency, Health Support Services, spent $154.7m on “computer services” in a single year. The real spend hides under labels like “computer” and “professional” services.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
@@ -1858,17 +1846,17 @@
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>$220m to $274.8m</t>
+          <t>$7.3m reported vs $154.7m</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>2022 to 2026</t>
+          <t>2023 to 2025</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>WA Health/DoF HRMIS contract disclosures; iTnews (2022)</t>
+          <t>Report on Consultants (tabled paper 2905); 2024-25 agency annual reports</t>
         </is>
       </c>
       <c r="J24" s="7" t="inlineStr">
@@ -1884,34 +1872,34 @@
       <c r="L24" s="9" t="inlineStr"/>
       <c r="M24" s="6" t="inlineStr">
         <is>
-          <t>$274.8m is a moving figure; re-confirm at point of use.</t>
+          <t>The $7.3m-vs-$154.7m contrast is a moving figure; re-confirm at point of use.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>B5</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>GovNext-ICT, the $65m savings that never came</t>
+          <t>The one lever for the regions, removed: aged-care place allocation</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>The GovNext-ICT program was sold on projected savings of $65m.</t>
+          <t>For decades the Commonwealth allocated residential aged-care places region by region against a planning ratio (a target of 78 places per 1,000 people aged 70 and over), the mechanism that steered new supply toward under-served country areas so a town was not left behind.</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>The Department of Premier and Cabinet accepted the AG's finding: “little doubt that the projected $65 million savings… will not be achieved.”</t>
+          <t>The ratio was lowered to 60.1 from 1 July 2024, and under the Places to People model the aged-care planning region ratio was discontinued altogether from late 2025, so a place now follows the individual into the market. That creates choice in a city with many providers and nothing in a town with none, because a place that follows a person is worthless where no operator will build. The Department's own material concedes competition will not exist universally. The one protection the regions had was removed, not replaced.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -1919,24 +1907,20 @@
           <t>IGNORED</t>
         </is>
       </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>$65m savings never realised</t>
-        </is>
-      </c>
+      <c r="G25" s="5" t="inlineStr"/>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2024 to 2025</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>WA Auditor General, Implementation of the GovNext-ICT Program</t>
-        </is>
-      </c>
-      <c r="J25" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>Australian Government Department of Health, Disability and Ageing, Places to People (residential aged care place allocation); Journal of Long-Term Care (2025), Regional Variation in Residential Aged Care Provision in Australia.</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="K25" s="8" t="inlineStr">
@@ -1945,141 +1929,448 @@
         </is>
       </c>
       <c r="L25" s="9" t="inlineStr"/>
-      <c r="M25" s="6" t="inlineStr"/>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>Commonwealth decision, not a State failure. The WA lever is to advocate a regional supply floor or loading and additionality in agreements. Confirm the exact 60.1 figure and the 1 November 2025 discontinuation date against the primary Department source before chamber use.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>D8</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>Office of Shared Services, ~$370m to unwind</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>WA's Office of Shared Services was sold as a savings program.</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
-        <is>
-          <t>Scrapped as a costly write-off: ~$370m to unwind after ~$258m had already been spent. Claimed savings became a loss.</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>IGNORED</t>
-        </is>
-      </c>
-      <c r="G26" s="5" t="inlineStr">
-        <is>
-          <t>~$370m to unwind</t>
-        </is>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>iTnews (2011), “WA to pay $370m to scrap shared services”</t>
-        </is>
-      </c>
-      <c r="J26" s="14" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>The answer already on the shelf: Aged Care Royal Commission recommendations WA has not been held to</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>The Royal Commission into Aged Care Quality and Safety handed down 148 recommendations in its 2021 Final Report, the national inquiry that already diagnosed the regional access problem and named the fixes, several on levers WA holds or can advocate (Multi-Purpose Services and cost-shared capital, a rural primary-care capitation model, specialist and geriatrician outreach, a properly costed viability supplement, and culturally appropriate advance-care processes and training on Country).</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>Five years on, WA's implementation status against these recommendations is not visible on the public record, and the one national mechanism that steered places to under-served regions was cut, then removed (see B5). The answer was delivered in 2021; the delivery was not.</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G26" s="11" t="inlineStr"/>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>2021 to 2026</t>
+        </is>
+      </c>
+      <c r="I26" s="12" t="inlineStr">
+        <is>
+          <t>Royal Commission into Aged Care Quality and Safety, Final Report Care, Dignity and Respect (2021), Recommendations 48, 51, 55, 56, 62, 113.</t>
+        </is>
+      </c>
+      <c r="J26" s="13" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="K26" s="8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L26" s="9" t="inlineStr"/>
-      <c r="M26" s="6" t="inlineStr"/>
+      <c r="K26" s="14" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="L26" s="12" t="inlineStr">
+        <is>
+          <t>Awaiting a Question on Notice on WA's implementation status for each named recommendation; flips to public once the reply lands.</t>
+        </is>
+      </c>
+      <c r="M26" s="12" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>WA's consultant shadow, $7.3m reported vs $154.7m real</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr">
-        <is>
-          <t>WA disclosed just $7.3m of whole-of-government “consultants” (six months to June 2023).</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>One agency, Health Support Services, spent $154.7m on “computer services” in a single year. The real spend hides under labels like “computer” and “professional” services.</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>RECURRING</t>
-        </is>
-      </c>
-      <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>$7.3m reported vs $154.7m</t>
-        </is>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>2023 to 2025</t>
-        </is>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>Report on Consultants (tabled paper 2905); 2024-25 agency annual reports</t>
-        </is>
-      </c>
-      <c r="J27" s="7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="K27" s="8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="L27" s="9" t="inlineStr"/>
-      <c r="M27" s="6" t="inlineStr">
-        <is>
-          <t>The $7.3m-vs-$154.7m contrast is a moving figure; re-confirm at point of use.</t>
-        </is>
-      </c>
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>The $100 million aged-care loan scheme: a regional promise, its own deadline, and the record</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Launching the $100 million Low-Interest Loan Scheme in January 2026, the Government said it would reach regional and remote areas, and committed that funding agreements would be announced and finalised by May 2026.</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>The May 2026 deadline passed with no date, funding figure or bed count given; providers who applied in February report no communication; the scheme is expected to deliver around 500 beds against a shortfall of up to 2,700; and the regional versus metropolitan split of applications, approvals and projected beds is not published.</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G27" s="11" t="inlineStr">
+        <is>
+          <t>$100m</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="I27" s="12" t="inlineStr">
+        <is>
+          <t>WA Government media statement (January 2026); Legislative Assembly questions without notice (2026); office at-a-glance brief.</t>
+        </is>
+      </c>
+      <c r="J27" s="13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="K27" s="14" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="L27" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the January 2026 verbatim and speaking minister against the primary release, and lodge the regional-split Question on Notice; flips to public when the reply or the primary lands.</t>
+        </is>
+      </c>
+      <c r="M27" s="12" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>Three years on from the Auditor General: older patients still stranded in hospital</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>The WA Auditor General identified that older long-stay patients were being held in hospital beds for want of a residential aged-care place to move to, and quantified the cost.</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>Around 200 elderly people remain stranded in hospital beds, and the problem the watchdog documented is still unresolved years on.</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G28" s="11" t="inlineStr"/>
+      <c r="H28" s="11" t="inlineStr">
+        <is>
+          <t>2022 to 2026</t>
+        </is>
+      </c>
+      <c r="I28" s="12" t="inlineStr">
+        <is>
+          <t>WA Auditor General (confirm the exact report and year); Legislative Assembly record (2025).</t>
+        </is>
+      </c>
+      <c r="J28" s="13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="K28" s="14" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="L28" s="12" t="inlineStr">
+        <is>
+          <t>Pin the exact AG report number, year and figures (patients, bed-days, cost) before public use.</t>
+        </is>
+      </c>
+      <c r="M28" s="12" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>A9</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>Urgent care clinics: a written promise with no towns, timeline or funding</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>The Government committed in writing, in February, to deliver urgent care clinics.</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>No towns, timeline or funding have been delivered against the written commitment.</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G29" s="11" t="inlineStr"/>
+      <c r="H29" s="11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I29" s="12" t="inlineStr">
+        <is>
+          <t>Government commitment (February); Legislative Assembly record (2025).</t>
+        </is>
+      </c>
+      <c r="J29" s="13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="K29" s="14" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="L29" s="12" t="inlineStr">
+        <is>
+          <t>Pin the written February commitment before public use.</t>
+        </is>
+      </c>
+      <c r="M29" s="12" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>Election promises missing from the budget papers</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>Named election commitments should appear, and be funded, in the budget papers.</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>Several named commitments cannot be located in the budget, and at least one is confirmed unfunded.</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G30" s="11" t="inlineStr"/>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I30" s="12" t="inlineStr">
+        <is>
+          <t>Question on Notice (2025); WA Budget Papers.</t>
+        </is>
+      </c>
+      <c r="J30" s="13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="K30" s="14" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="L30" s="12" t="inlineStr">
+        <is>
+          <t>Pin each named promise to the relevant budget line, or its absence, before public use.</t>
+        </is>
+      </c>
+      <c r="M30" s="12" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>Softwood plantation expansion delivered at six per cent, then the target reframed</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>The Government promised a $350 million, 35,000 hectare softwood plantation expansion to secure the timber estate.</t>
+        </is>
+      </c>
+      <c r="E31" s="12" t="inlineStr">
+        <is>
+          <t>The program was delivered at around six per cent of the hectare target, and the target was reframed downward rather than confirmed.</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G31" s="11" t="inlineStr">
+        <is>
+          <t>$350m</t>
+        </is>
+      </c>
+      <c r="H31" s="11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I31" s="12" t="inlineStr">
+        <is>
+          <t>Question on Notice 453 (2025).</t>
+        </is>
+      </c>
+      <c r="J31" s="13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="K31" s="14" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="L31" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the Question on Notice 453 answer figures before public use.</t>
+        </is>
+      </c>
+      <c r="M31" s="12" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t>A12</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>A public accountability measure retired as the estate took a drought hit</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>A public thinning-timeliness performance measure existed for the softwood estate, the yardstick for whether it was managed on time.</t>
+        </is>
+      </c>
+      <c r="E32" s="12" t="inlineStr">
+        <is>
+          <t>The Government confirmed it will not reinstate the measure, just as the estate absorbed a reported $29 million drought loss.</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>UNVERIFIED</t>
+        </is>
+      </c>
+      <c r="G32" s="11" t="inlineStr">
+        <is>
+          <t>$29m</t>
+        </is>
+      </c>
+      <c r="H32" s="11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="I32" s="12" t="inlineStr">
+        <is>
+          <t>Question on Notice 1022 (2025).</t>
+        </is>
+      </c>
+      <c r="J32" s="13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="K32" s="14" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="L32" s="12" t="inlineStr">
+        <is>
+          <t>Confirm the Question on Notice 1022 answer before public use.</t>
+        </is>
+      </c>
+      <c r="M32" s="12" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:M27"/>
+  <autoFilter ref="A3:M32"/>
   <mergeCells count="2">
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A1:M1"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F4:F27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="F4:F32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"DONE,PARTIAL,IGNORED,RECURRING,OVERDUE,UNVERIFIED"</formula1>
     </dataValidation>
-    <dataValidation sqref="J4:J27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation sqref="J4:J32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"HIGH,MEDIUM,LOW"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2230,7 +2521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2264,7 +2555,7 @@
       </c>
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t>A documented warning, harm that followed, and the costly patch. Some entries are live and flagged unverified.</t>
+          <t>A documented warning, the harm that followed, and the costly patch. Every entry here is verified and sourced.</t>
         </is>
       </c>
     </row>
@@ -2276,7 +2567,7 @@
       </c>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t>A “we consulted” claim turned into a checkable record. Most WA cases here are not yet verified, shown honestly.</t>
+          <t>A “we consulted” claim turned into a checkable record. Every WA case here is verified to a primary source.</t>
         </is>
       </c>
     </row>
@@ -2362,108 +2653,120 @@
     <row r="13">
       <c r="A13" s="19" t="inlineStr">
         <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>An open, ongoing matter that is verified but not yet decided; shown flagged, never as settled.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
           <t>UNVERIFIED</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>Not yet confirmed to a primary source, or a live matter not yet decided.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>Not yet confirmed to a primary source.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>Confidence values</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="19" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>Confirmed to a primary source; safe to use.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="19" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="B17" s="17" t="inlineStr">
         <is>
-          <t>Sourced but with a caveat noted in `notes`; confirm at point of use.</t>
+          <t>Confirmed to a primary source; safe to use.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
         <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>Sourced but with a caveat noted in `notes`; confirm at point of use.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>Weak or single-thread sourcing; must not be used publicly until strengthened.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>The discipline</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="19" t="inlineStr">
-        <is>
-          <t>direction</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="inlineStr">
-        <is>
-          <t>Radical transparency pointed upward at power, not downward at the public. Holds recommendations, not people.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="19" t="inlineStr">
         <is>
-          <t>robodebt_guardrail</t>
+          <t>direction</t>
         </is>
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>No personal data, no algorithm over any citizen, no automated decision about anyone. The opposite of Robodebt, on purpose.</t>
+          <t>Radical transparency pointed upward at power, not downward at the public. Holds recommendations, not people.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>enforcement</t>
+          <t>robodebt_guardrail</t>
         </is>
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>Check the ledger before you write the cheque: any business case to commission external research/consultancy must first cite the ledger and show the question is genuinely unanswered, or state on the record why it departs from what was already recommended.</t>
+          <t>No personal data, no algorithm over any citizen, no automated decision about anyone. The opposite of Robodebt, on purpose.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="19" t="inlineStr">
         <is>
+          <t>enforcement</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>Check the ledger before you write the cheque: any business case to commission external research/consultancy must first cite the ledger and show the question is genuinely unanswered, or state on the record why it departs from what was already recommended.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
           <t>honesty_rule</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B25" s="17" t="inlineStr">
         <is>
           <t>Every figure carries a source and a confidence flag. Figures are never summed, each has its own source. Entries with status UNVERIFIED or confidence LOW are withheld from public use (public_use=false) and flagged HOLD.</t>
         </is>

--- a/views/open_accountability_ledger.xlsx
+++ b/views/open_accountability_ledger.xlsx
@@ -563,7 +563,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Open Accountability Ledger — register v0.4.0 · build-phase demonstrator, internal, not for publication</t>
+          <t>Open Accountability Ledger — register v0.4.1 · build-phase demonstrator, internal, not for publication</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1899,7 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>The ratio was lowered to 60.1 from 1 July 2024, and under the Places to People model the aged-care planning region ratio was discontinued altogether from late 2025, so a place now follows the individual into the market. That creates choice in a city with many providers and nothing in a town with none, because a place that follows a person is worthless where no operator will build. The Department's own material concedes competition will not exist universally. The one protection the regions had was removed, not replaced.</t>
+          <t>The ratio was lowered to 60.1 from 1 July 2024, and under the Places to People model the aged-care planning region ratio was discontinued altogether from late 2025, so a place now follows the individual into the market. That creates choice in a city with many providers and nothing in a town with none, because a place that follows a person is worthless where no operator will build. The Department concedes competition will not exist universally. The one protection the regions had was removed, not replaced.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>The Royal Commission into Aged Care Quality and Safety handed down 148 recommendations in its 2021 Final Report, the national inquiry that already diagnosed the regional access problem and named the fixes, several on levers WA holds or can advocate (Multi-Purpose Services and cost-shared capital, a rural primary-care capitation model, specialist and geriatrician outreach, a properly costed viability supplement, and culturally appropriate advance-care processes and training on Country).</t>
+          <t>The Royal Commission into Aged Care Quality and Safety handed down 148 recommendations in its 2021 Final Report, several on levers WA holds or can advocate (Multi-Purpose Services and cost-shared capital, a rural primary-care capitation model, specialist and geriatrician outreach, a properly costed viability supplement, and culturally appropriate advance-care processes and training on Country).</t>
         </is>
       </c>
       <c r="E26" s="12" t="inlineStr">
         <is>
-          <t>Five years on, WA's implementation status against these recommendations is not visible on the public record, and the one national mechanism that steered places to under-served regions was cut, then removed (see B5). The answer was delivered in 2021; the delivery was not.</t>
+          <t>Five years on, WA's implementation status against these recommendations is not visible on the public record, and the national mechanism that steered places to under-served regions was cut, then removed (see B5). The answer was delivered in 2021; the delivery is not on the record.</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr">
@@ -1989,132 +1989,128 @@
       </c>
       <c r="L26" s="12" t="inlineStr">
         <is>
-          <t>Awaiting a Question on Notice on WA's implementation status for each named recommendation; flips to public once the reply lands.</t>
+          <t>The recommendations are verified; WA's implementation status is the open question. Lodge a Question on Notice on WA's status per named recommendation; flips to public once the reply lands.</t>
         </is>
       </c>
       <c r="M26" s="12" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>A7</t>
         </is>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>The $100 million aged-care loan scheme: a regional promise, its own deadline, and the record</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>Launching the $100 million Low-Interest Loan Scheme in January 2026, the Government said it would reach regional and remote areas, and committed that funding agreements would be announced and finalised by May 2026.</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>The May 2026 deadline passed with no date, funding figure or bed count given; providers who applied in February report no communication; the scheme is expected to deliver around 500 beds against a shortfall of up to 2,700; and the regional versus metropolitan split of applications, approvals and projected beds is not published.</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="inlineStr">
-        <is>
-          <t>UNVERIFIED</t>
-        </is>
-      </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>The $100 million aged-care loan scheme missed its own deadline</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>The WA Government's $100 million Aged Care Low Interest Loan Scheme committed that funding agreements would be announced and finalised by May 2026.</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>On 18 June 2026 the responsible minister confirmed the May 2026 deadline had passed without the applicants, the total value of funding, or the number and timing of new beds being announced. The regional versus metropolitan split of applications and projected beds is not published.</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>OVERDUE</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
         <is>
           <t>$100m</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="I27" s="12" t="inlineStr">
-        <is>
-          <t>WA Government media statement (January 2026); Legislative Assembly questions without notice (2026); office at-a-glance brief.</t>
-        </is>
-      </c>
-      <c r="J27" s="13" t="inlineStr">
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>WA Government, Aged Care Low Interest Loan Scheme (https://www.wa.gov.au/organisation/department-of-energy-and-economic-diversification/aged-care-low-interest-loan-scheme); WA Legislative Assembly, 18 June 2026.</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="K27" s="14" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="L27" s="12" t="inlineStr">
-        <is>
-          <t>Confirm the January 2026 verbatim and speaking minister against the primary release, and lodge the regional-split Question on Notice; flips to public when the reply or the primary lands.</t>
-        </is>
-      </c>
-      <c r="M27" s="12" t="inlineStr"/>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L27" s="9" t="inlineStr"/>
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t>The deadline miss and the absence of figures are on the Assembly record. Confirm the exact May 2026 commitment wording against the scheme page, and lodge the regional-split Question on Notice, before leaning on the regional-and-remote angle.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>A8</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C28" s="12" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>Three years on from the Auditor General: older patients still stranded in hospital</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>The WA Auditor General identified that older long-stay patients were being held in hospital beds for want of a residential aged-care place to move to, and quantified the cost.</t>
-        </is>
-      </c>
-      <c r="E28" s="12" t="inlineStr">
-        <is>
-          <t>Around 200 elderly people remain stranded in hospital beds, and the problem the watchdog documented is still unresolved years on.</t>
-        </is>
-      </c>
-      <c r="F28" s="11" t="inlineStr">
-        <is>
-          <t>UNVERIFIED</t>
-        </is>
-      </c>
-      <c r="G28" s="11" t="inlineStr"/>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>In November 2022 the WA Auditor General found the State had no effective system for managing long-stay patients, reporting that 486 patients spent a combined 40,000 unnecessary days in hospital at a cost of about $95 million, with regional patients waiting around 50 days against 11.4 in Perth.</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>Nearly three years on, about 200 elderly Western Australians remain stranded in public hospitals, medically cleared but with nowhere to go, and the system the watchdog said to fix is still not fixed.</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>IGNORED</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr">
         <is>
           <t>2022 to 2026</t>
         </is>
       </c>
-      <c r="I28" s="12" t="inlineStr">
-        <is>
-          <t>WA Auditor General (confirm the exact report and year); Legislative Assembly record (2025).</t>
-        </is>
-      </c>
-      <c r="J28" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="K28" s="14" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="L28" s="12" t="inlineStr">
-        <is>
-          <t>Pin the exact AG report number, year and figures (patients, bed-days, cost) before public use.</t>
-        </is>
-      </c>
-      <c r="M28" s="12" t="inlineStr"/>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>WA Auditor General, Management of Long Stay Patients in Public Hospitals, Report 9 (November 2022) (https://audit.wa.gov.au/reports-and-publications/reports/management-of-long-stay-patients-in-public-hospitals/); figures restated in WA Legislative Assembly, 19 August 2025.</t>
+        </is>
+      </c>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L28" s="9" t="inlineStr"/>
+      <c r="M28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="11" t="inlineStr">
@@ -2134,12 +2130,12 @@
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>The Government committed in writing, in February, to deliver urgent care clinics.</t>
+          <t>In February the Government promised in writing to deliver urgent care clinics across the South West, including Warren-Blackwood, to relieve pressure on emergency departments.</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>No towns, timeline or funding have been delivered against the written commitment.</t>
+          <t>With the 2025-26 budget handed down there was still no detail on which towns, what timeline, or what funding.</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr">
@@ -2155,7 +2151,7 @@
       </c>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>Government commitment (February); Legislative Assembly record (2025).</t>
+          <t>WA Legislative Assembly, 13 August 2025 (referencing the February written commitment).</t>
         </is>
       </c>
       <c r="J29" s="13" t="inlineStr">
@@ -2170,195 +2166,187 @@
       </c>
       <c r="L29" s="12" t="inlineStr">
         <is>
-          <t>Pin the written February commitment before public use.</t>
+          <t>The Assembly reference is on the record; pin the actual February written commitment (the primary) before public use.</t>
         </is>
       </c>
       <c r="M29" s="12" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>A10</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>Election promises missing from the budget papers</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>Named election commitments should appear, and be funded, in the budget papers.</t>
-        </is>
-      </c>
-      <c r="E30" s="12" t="inlineStr">
-        <is>
-          <t>Several named commitments cannot be located in the budget, and at least one is confirmed unfunded.</t>
-        </is>
-      </c>
-      <c r="F30" s="11" t="inlineStr">
-        <is>
-          <t>UNVERIFIED</t>
-        </is>
-      </c>
-      <c r="G30" s="11" t="inlineStr"/>
-      <c r="H30" s="11" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Six named election commitments were put to the Government to locate in the budget papers, including the Boyup Brook Recreation Centre, the Denmark Primary School car park, the Manjimup Rea Park redevelopment, the Margaret River fire station and regional childcare support.</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>The Government confirmed the Boyup Brook Recreation Centre is not funded and left several named promises without a budget location, while confirming $5.1 million each for the Margaret River fire station and regional childcare.</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>IGNORED</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="I30" s="12" t="inlineStr">
-        <is>
-          <t>Question on Notice (2025); WA Budget Papers.</t>
-        </is>
-      </c>
-      <c r="J30" s="13" t="inlineStr">
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>WA Legislative Assembly, Question on Notice 439, answered 16 September 2025 (https://www.parliament.wa.gov.au/parliament/pquest.nsf/viewLAPQuestByDate/A19AA726E84C14BD48258CDF0038EF8C?opendocument).</t>
+        </is>
+      </c>
+      <c r="J30" s="10" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="K30" s="14" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="L30" s="12" t="inlineStr">
-        <is>
-          <t>Pin each named promise to the relevant budget line, or its absence, before public use.</t>
-        </is>
-      </c>
-      <c r="M30" s="12" t="inlineStr"/>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L30" s="9" t="inlineStr"/>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>Confirmed unfunded item is the Boyup Brook Recreation Centre; treat the other unlocated promises as unlocated, not as confirmed cut.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>A11</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>Softwood plantation expansion delivered at six per cent, then the target reframed</t>
-        </is>
-      </c>
-      <c r="D31" s="12" t="inlineStr">
-        <is>
-          <t>The Government promised a $350 million, 35,000 hectare softwood plantation expansion to secure the timber estate.</t>
-        </is>
-      </c>
-      <c r="E31" s="12" t="inlineStr">
-        <is>
-          <t>The program was delivered at around six per cent of the hectare target, and the target was reframed downward rather than confirmed.</t>
-        </is>
-      </c>
-      <c r="F31" s="11" t="inlineStr">
-        <is>
-          <t>UNVERIFIED</t>
-        </is>
-      </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Softwood plantation expansion delivered at a fraction, then the target reframed</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>The Government promised a $350 million softwood plantation expansion of 35,000 hectares to secure the timber estate.</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>After three years the Government reframed the program as a record $350 million over ten years, said about 20,000 to 25,000 hectares is likely if focused on freehold land, and reported 1,538 hectares established through joint ventures. It did not commit to the original 35,000 hectare target.</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>IGNORED</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>$350m</t>
         </is>
       </c>
-      <c r="H31" s="11" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="I31" s="12" t="inlineStr">
-        <is>
-          <t>Question on Notice 453 (2025).</t>
-        </is>
-      </c>
-      <c r="J31" s="13" t="inlineStr">
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>WA Legislative Assembly, Question on Notice 453, answered 16 September 2025 (https://www.parliament.wa.gov.au/parliament/pquest.nsf/viewLAPQuestByDate/4F9A6BDD9F1DB89748258CE4002749F2?opendocument).</t>
+        </is>
+      </c>
+      <c r="J31" s="10" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="K31" s="14" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="L31" s="12" t="inlineStr">
-        <is>
-          <t>Confirm the Question on Notice 453 answer figures before public use.</t>
-        </is>
-      </c>
-      <c r="M31" s="12" t="inlineStr"/>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L31" s="9" t="inlineStr"/>
+      <c r="M31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>A12</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>A public accountability measure retired as the estate took a drought hit</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>A public thinning-timeliness performance measure existed for the softwood estate, the yardstick for whether it was managed on time.</t>
-        </is>
-      </c>
-      <c r="E32" s="12" t="inlineStr">
-        <is>
-          <t>The Government confirmed it will not reinstate the measure, just as the estate absorbed a reported $29 million drought loss.</t>
-        </is>
-      </c>
-      <c r="F32" s="11" t="inlineStr">
-        <is>
-          <t>UNVERIFIED</t>
-        </is>
-      </c>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>The softwood estate carried a public thinning-timeliness performance measure, the yardstick for whether it was being managed on time.</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>The Government confirmed about 1,500 hectares in the South-West and 6,000 in the Mid-West were significantly affected by drought, with a roughly $29 million negative impact on plantation value, and that it will not reinstate the thinning timeliness measure.</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>IGNORED</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
         <is>
           <t>$29m</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="I32" s="12" t="inlineStr">
-        <is>
-          <t>Question on Notice 1022 (2025).</t>
-        </is>
-      </c>
-      <c r="J32" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="K32" s="14" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="L32" s="12" t="inlineStr">
-        <is>
-          <t>Confirm the Question on Notice 1022 answer before public use.</t>
-        </is>
-      </c>
-      <c r="M32" s="12" t="inlineStr"/>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>WA Legislative Assembly, Question on Notice 1022, answered 16 December 2025 (https://www.parliament.wa.gov.au/parliament/pquest.nsf/viewLAPQuestByDate/DD891B31148789DE48258D4000371DC0?opendocument).</t>
+        </is>
+      </c>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="L32" s="9" t="inlineStr"/>
+      <c r="M32" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:M32"/>
